--- a/data/processed/harmonization/Major_and_trace_elements_total__Total_cadmium/harmonized.xlsx
+++ b/data/processed/harmonization/Major_and_trace_elements_total__Total_cadmium/harmonized.xlsx
@@ -426,13 +426,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L287"/>
+  <dimension ref="A1:L293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="47" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>4:20-29</t>
+          <t>Hu:4:20-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -553,7 +553,7 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -570,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>4:10-20</t>
+          <t>Hu:4:10-20</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -605,7 +605,7 @@
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4:0-10</t>
+          <t>Hu:4:0-10</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -657,7 +657,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -674,12 +674,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4:-10-0</t>
+          <t>Ho:4:-10-0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4:-20--10</t>
+          <t>Ho:4:-20--10</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4:-30--20</t>
+          <t>Ho:4:-30--20</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -969,7 +969,7 @@
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4:-80--70</t>
+          <t>Ho:4:-80--70</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4:-100--90</t>
+          <t>Ho:4:-100--90</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4:-150--125</t>
+          <t>Ho:4:-150--125</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1333,7 +1333,7 @@
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4:-200--175</t>
+          <t>Ho:4:-200--175</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4:-250--200</t>
+          <t>Ho:4:-250--200</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5:0-24</t>
+          <t>Hu:5:0-24</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5:10-18</t>
+          <t>Hu:5:10-18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5:0-10</t>
+          <t>Hu:5:0-10</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1593,7 +1593,7 @@
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5:-10-0</t>
+          <t>Ho:5:-10-0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5:-20--10</t>
+          <t>Ho:5:-20--10</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1697,7 +1697,7 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5:-30--20</t>
+          <t>Ho:5:-30--20</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1749,7 +1749,7 @@
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1818,12 +1818,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1853,7 +1853,7 @@
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5:-80--70</t>
+          <t>Ho:5:-80--70</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2061,7 +2061,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2078,12 +2078,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>5:-100--90</t>
+          <t>Ho:5:-100--90</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>5:-150--125</t>
+          <t>Ho:5:-150--125</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>5:-200--175</t>
+          <t>Ho:5:-200--175</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>5:-250--200</t>
+          <t>Ho:5:-250--200</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>5:-300--250</t>
+          <t>Ho:5:-300--250</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>6:20-30</t>
+          <t>Hu:6:20-30</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>6:-10-0</t>
+          <t>Ho:6:-10-0</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>6:-20--10</t>
+          <t>Ho:6:-20--10</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2702,12 +2702,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>6:-30--20</t>
+          <t>Ho:6:-30--20</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2737,7 +2737,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2754,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>6:-40--30</t>
+          <t>Ho:6:-40--30</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2789,7 +2789,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2806,12 +2806,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>6:-50--40</t>
+          <t>Ho:6:-50--40</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2858,12 +2858,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>6:-60--50</t>
+          <t>Ho:6:-60--50</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2893,7 +2893,7 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2910,12 +2910,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>6:-70--60</t>
+          <t>Ho:6:-70--60</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>6:-80--70</t>
+          <t>Ho:6:-80--70</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2997,7 +2997,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>6:-90--80</t>
+          <t>Ho:6:-90--80</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>6:-100--90</t>
+          <t>Ho:6:-100--90</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3101,7 +3101,7 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>6:-125--100</t>
+          <t>Ho:6:-125--100</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>6:-150--125</t>
+          <t>Ho:6:-150--125</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>6:-175--150</t>
+          <t>Ho:6:-175--150</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3257,7 +3257,7 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>6:-200--175</t>
+          <t>Ho:6:-200--175</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3309,7 +3309,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>6:-250--200</t>
+          <t>Ho:6:-250--200</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3378,12 +3378,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3430,12 +3430,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>7:20-22</t>
+          <t>Hu:7:20-22</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3465,7 +3465,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>7:10-20</t>
+          <t>Hu:7:10-20</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3534,12 +3534,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>7:-10-0</t>
+          <t>Ho:7:-10-0</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3569,7 +3569,7 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3586,12 +3586,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>7:-20--10</t>
+          <t>Ho:7:-20--10</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3621,7 +3621,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>7:-30--20</t>
+          <t>Ho:7:-30--20</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3673,7 +3673,7 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>7:-40--30</t>
+          <t>Ho:7:-40--30</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3725,7 +3725,7 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>7:-50--40</t>
+          <t>Ho:7:-50--40</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>7:-60--50</t>
+          <t>Ho:7:-60--50</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>7:-70--60</t>
+          <t>Ho:7:-70--60</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3898,12 +3898,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>7:-80--70</t>
+          <t>Ho:7:-80--70</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>7:-90--80</t>
+          <t>Ho:7:-90--80</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4002,12 +4002,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>7:-100--90</t>
+          <t>Ho:7:-100--90</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4037,7 +4037,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>7:-125--100</t>
+          <t>Ho:7:-125--100</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4089,7 +4089,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4106,12 +4106,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>7:-150--125</t>
+          <t>Ho:7:-150--125</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>7:-175--150</t>
+          <t>Ho:7:-175--150</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4193,7 +4193,7 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4210,12 +4210,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>7:-200--175</t>
+          <t>Ho:7:-200--175</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4245,7 +4245,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4262,12 +4262,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>7:-250--200</t>
+          <t>Ho:7:-250--200</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4314,12 +4314,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>7:-300--250</t>
+          <t>Ho:7:-300--250</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>8:10-20</t>
+          <t>Hu:8:10-20</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>8:0-10</t>
+          <t>Hu:8:0-10</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Hu:8:-10-0</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4505,7 +4505,7 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4522,17 +4522,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>8:-20--10</t>
+          <t>Ho:8:-10-0</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>-20--10</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4557,7 +4557,7 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4574,17 +4574,17 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>8:-30--20</t>
+          <t>Ho:8:-20--10</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>-30--20</t>
+          <t>-20--10</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4609,7 +4609,7 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4626,17 +4626,17 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>8:-40--30</t>
+          <t>Ho:8:-30--20</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>-40--30</t>
+          <t>-30--20</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4678,17 +4678,17 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>8:-50--40</t>
+          <t>Ho:8:-40--30</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>-50--40</t>
+          <t>-40--30</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4713,7 +4713,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4730,17 +4730,17 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>8:-60--50</t>
+          <t>Ho:8:-50--40</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>-60--50</t>
+          <t>-50--40</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4782,17 +4782,17 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>8:-70--60</t>
+          <t>Ho:8:-60--50</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>-70--60</t>
+          <t>-60--50</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4834,17 +4834,17 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>8:-80--70</t>
+          <t>Ho:8:-70--60</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>-80--70</t>
+          <t>-70--60</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4886,17 +4886,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>8:-90--80</t>
+          <t>Ho:8:-80--70</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>-90--80</t>
+          <t>-80--70</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4938,17 +4938,17 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>8:-100--90</t>
+          <t>Ho:8:-90--80</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>-100--90</t>
+          <t>-90--80</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -4973,7 +4973,7 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4990,17 +4990,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>8:-125--100</t>
+          <t>Ho:8:-100--90</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>-125--100</t>
+          <t>-100--90</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5042,17 +5042,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>8:-150--125</t>
+          <t>Ho:8:-125--100</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>-150--125</t>
+          <t>-125--100</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5094,17 +5094,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>8:-175--150</t>
+          <t>Ho:8:-150--125</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>-175--150</t>
+          <t>-150--125</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -5129,7 +5129,7 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5146,17 +5146,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>8:-200--175</t>
+          <t>Ho:8:-175--150</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>-200--175</t>
+          <t>-175--150</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5198,17 +5198,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>9:10-18</t>
+          <t>Ho:8:-200--175</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>10-18</t>
+          <t>-200--175</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5250,17 +5250,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>9:0-10</t>
+          <t>Hu:9:10-18</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-18</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -5285,7 +5285,7 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5302,17 +5302,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>9:-10-0</t>
+          <t>Hu:9:0-10</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>-10-0</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5354,17 +5354,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>9:-20--10</t>
+          <t>Ho:9:-10-0</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>-20--10</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5406,17 +5406,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>9:-30--20</t>
+          <t>Ho:9:-20--10</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>-30--20</t>
+          <t>-20--10</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5458,17 +5458,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>9:-40--30</t>
+          <t>Ho:9:-30--20</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>-40--30</t>
+          <t>-30--20</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -5493,7 +5493,7 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5510,17 +5510,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>9:-50--40</t>
+          <t>Ho:9:-40--30</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>-50--40</t>
+          <t>-40--30</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5562,17 +5562,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>9:-60--50</t>
+          <t>Ho:9:-50--40</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>-60--50</t>
+          <t>-50--40</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5614,17 +5614,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>9:-70--60</t>
+          <t>Ho:9:-60--50</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>-70--60</t>
+          <t>-60--50</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -5649,7 +5649,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5666,17 +5666,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>9:-80--70</t>
+          <t>Ho:9:-70--60</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>-80--70</t>
+          <t>-70--60</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -5701,7 +5701,7 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5718,17 +5718,17 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>9:-90--80</t>
+          <t>Ho:9:-80--70</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>-90--80</t>
+          <t>-80--70</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -5753,7 +5753,7 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5770,17 +5770,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>9:-100--90</t>
+          <t>Ho:9:-90--80</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>-100--90</t>
+          <t>-90--80</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -5805,7 +5805,7 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5822,17 +5822,17 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>9:-125--100</t>
+          <t>Ho:9:-100--90</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>-125--100</t>
+          <t>-100--90</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5857,7 +5857,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5874,17 +5874,17 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>9:-150--125</t>
+          <t>Ho:9:-125--100</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>-150--125</t>
+          <t>-125--100</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -5909,7 +5909,7 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5926,17 +5926,17 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>9:-175--150</t>
+          <t>Ho:9:-150--125</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>-175--150</t>
+          <t>-150--125</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -5961,7 +5961,7 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5978,17 +5978,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>9:-200--175</t>
+          <t>Ho:9:-175--150</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>-200--175</t>
+          <t>-175--150</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>9:-250--200</t>
+          <t>Ho:9:-200--175</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>-250--200</t>
+          <t>-200--175</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -6065,7 +6065,7 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6082,17 +6082,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>9:-300--250</t>
+          <t>Ho:9:-250--200</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>-300--250</t>
+          <t>-250--200</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6134,17 +6134,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>10:20-29</t>
+          <t>Ho:9:-300--250</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>20-29</t>
+          <t>-300--250</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6186,17 +6186,17 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>10:10-20</t>
+          <t>Hu:10:20-29</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6238,17 +6238,17 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>10:0-10</t>
+          <t>Hu:10:10-20</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -6273,7 +6273,7 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6290,17 +6290,17 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>10:-10-0</t>
+          <t>Hu:10:0-10</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>-10-0</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6342,17 +6342,17 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>10:-20--10</t>
+          <t>Ho:10:-10-0</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>-20--10</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6394,17 +6394,17 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>10:-30--20</t>
+          <t>Ho:10:-20--10</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>-30--20</t>
+          <t>-20--10</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -6429,7 +6429,7 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6446,17 +6446,17 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>10:-40--30</t>
+          <t>Ho:10:-30--20</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>-40--30</t>
+          <t>-30--20</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6498,17 +6498,17 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>10:-50--40</t>
+          <t>Ho:10:-40--30</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>-50--40</t>
+          <t>-40--30</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6550,17 +6550,17 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>10:-60--50</t>
+          <t>Ho:10:-50--40</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>-60--50</t>
+          <t>-50--40</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6602,17 +6602,17 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>10:-70--60</t>
+          <t>Ho:10:-60--50</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>-70--60</t>
+          <t>-60--50</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -6637,7 +6637,7 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6654,17 +6654,17 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>10:-80--70</t>
+          <t>Ho:10:-70--60</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>-80--70</t>
+          <t>-70--60</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6706,17 +6706,17 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>10:-90--80</t>
+          <t>Ho:10:-80--70</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>-90--80</t>
+          <t>-80--70</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -6741,7 +6741,7 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6758,17 +6758,17 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>10:-100--90</t>
+          <t>Ho:10:-90--80</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>-100--90</t>
+          <t>-90--80</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -6793,7 +6793,7 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6810,17 +6810,17 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>10:-125--100</t>
+          <t>Ho:10:-100--90</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>-125--100</t>
+          <t>-100--90</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6862,17 +6862,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>10:-150--125</t>
+          <t>Ho:10:-125--100</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>-150--125</t>
+          <t>-125--100</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -6897,7 +6897,7 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6914,17 +6914,17 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>10:-175--150</t>
+          <t>Ho:10:-150--125</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>-175--150</t>
+          <t>-150--125</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6966,17 +6966,17 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>10:-200--175</t>
+          <t>Ho:10:-175--150</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>-200--175</t>
+          <t>-175--150</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7018,17 +7018,17 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>10:-225--200</t>
+          <t>Ho:10:-200--175</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>-225--200</t>
+          <t>-200--175</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7070,17 +7070,17 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>10:-255--225</t>
+          <t>Ho:10:-225--200</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>-255--225</t>
+          <t>-225--200</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -7105,7 +7105,7 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7122,17 +7122,17 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>10:-275--255</t>
+          <t>Ho:10:-255--225</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>-275--255</t>
+          <t>-255--225</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7174,17 +7174,17 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>11:10-18</t>
+          <t>Ho:10:-275--255</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>10-18</t>
+          <t>-275--255</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7226,17 +7226,17 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>11:0-10</t>
+          <t>Hu:11:10-18</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-18</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -7261,7 +7261,7 @@
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7278,17 +7278,17 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>11:-10-0</t>
+          <t>Hu:11:0-10</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>-10-0</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7330,17 +7330,17 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>11:-20--10</t>
+          <t>Ho:11:-10-0</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>-20--10</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -7365,7 +7365,7 @@
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7382,17 +7382,17 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>11:-30--20</t>
+          <t>Ho:11:-20--10</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>-30--20</t>
+          <t>-20--10</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7434,17 +7434,17 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>11:-40--30</t>
+          <t>Ho:11:-30--20</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>-40--30</t>
+          <t>-30--20</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7486,17 +7486,17 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>11:-50--40</t>
+          <t>Ho:11:-40--30</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>-50--40</t>
+          <t>-40--30</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7538,17 +7538,17 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>11:-60--50</t>
+          <t>Ho:11:-50--40</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>-60--50</t>
+          <t>-50--40</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7590,17 +7590,17 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>11:-70--60</t>
+          <t>Ho:11:-60--50</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>-70--60</t>
+          <t>-60--50</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7642,17 +7642,17 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>11:-80--70</t>
+          <t>Ho:11:-70--60</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>-80--70</t>
+          <t>-70--60</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -7677,7 +7677,7 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7694,17 +7694,17 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>11:-90--80</t>
+          <t>Ho:11:-80--70</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>-90--80</t>
+          <t>-80--70</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -7729,7 +7729,7 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7746,17 +7746,17 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>11:-100--90</t>
+          <t>Ho:11:-90--80</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>-100--90</t>
+          <t>-90--80</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -7781,7 +7781,7 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7798,17 +7798,17 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>11:-125--100</t>
+          <t>Ho:11:-100--90</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>-125--100</t>
+          <t>-100--90</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -7833,7 +7833,7 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7850,17 +7850,17 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>11:-150--125</t>
+          <t>Ho:11:-125--100</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>-150--125</t>
+          <t>-125--100</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7902,17 +7902,17 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>11:-175--150</t>
+          <t>Ho:11:-150--125</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>-175--150</t>
+          <t>-150--125</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -7937,7 +7937,7 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7954,17 +7954,17 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>11:-200--175</t>
+          <t>Ho:11:-175--150</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>-200--175</t>
+          <t>-175--150</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -7989,7 +7989,7 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8006,17 +8006,17 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>11:-250--200</t>
+          <t>Ho:11:-200--175</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>-250--200</t>
+          <t>-200--175</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8058,17 +8058,17 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>13:20-25</t>
+          <t>Ho:11:-250--200</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>20-25</t>
+          <t>-250--200</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -8093,7 +8093,7 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8110,17 +8110,17 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>13:10-20</t>
+          <t>Hu:13:20-25</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-25</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8162,17 +8162,17 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>13:0-10</t>
+          <t>Hu:13:10-20</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -8197,7 +8197,7 @@
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8214,17 +8214,17 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Hu:13:0-10</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>-10-0</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -8249,7 +8249,7 @@
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8266,17 +8266,17 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>13:-20--10</t>
+          <t>Hu:13:-10-0</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>-20--10</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -8301,7 +8301,7 @@
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8318,17 +8318,17 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>13:-30--20</t>
+          <t>Ho:13:-10-0</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>-30--20</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -8353,7 +8353,7 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8370,17 +8370,17 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>13:-40--30</t>
+          <t>Ho:13:-20--10</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>-40--30</t>
+          <t>-20--10</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -8405,7 +8405,7 @@
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8422,17 +8422,17 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>13:-50--40</t>
+          <t>Ho:13:-30--20</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>-50--40</t>
+          <t>-30--20</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -8457,7 +8457,7 @@
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8474,17 +8474,17 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>13:-60--50</t>
+          <t>Ho:13:-40--30</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>-60--50</t>
+          <t>-40--30</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8526,17 +8526,17 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>13:-70--60</t>
+          <t>Ho:13:-50--40</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>-70--60</t>
+          <t>-50--40</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -8561,7 +8561,7 @@
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8578,17 +8578,17 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>13:-80--70</t>
+          <t>Ho:13:-60--50</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>-80--70</t>
+          <t>-60--50</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -8613,7 +8613,7 @@
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8630,17 +8630,17 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>13:-90--80</t>
+          <t>Ho:13:-70--60</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>-90--80</t>
+          <t>-70--60</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8682,17 +8682,17 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>13:-100--90</t>
+          <t>Ho:13:-80--70</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>-100--90</t>
+          <t>-80--70</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8734,17 +8734,17 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>13:-125--100</t>
+          <t>Ho:13:-90--80</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>-125--100</t>
+          <t>-90--80</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8786,17 +8786,17 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>13:-150--125</t>
+          <t>Ho:13:-100--90</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>-150--125</t>
+          <t>-100--90</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -8821,7 +8821,7 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8838,17 +8838,17 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>13:-175--150</t>
+          <t>Ho:13:-125--100</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>-175--150</t>
+          <t>-125--100</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -8873,7 +8873,7 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8890,17 +8890,17 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>13:-200--175</t>
+          <t>Ho:13:-150--125</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>-200--175</t>
+          <t>-150--125</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -8925,7 +8925,7 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8942,17 +8942,17 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>13:-250--200</t>
+          <t>Ho:13:-175--150</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>-250--200</t>
+          <t>-175--150</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -8977,7 +8977,7 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8994,17 +8994,17 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>13:-270--250</t>
+          <t>Ho:13:-200--175</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>-270--250</t>
+          <t>-200--175</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -9029,7 +9029,7 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9046,17 +9046,17 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>13:-300--270</t>
+          <t>Ho:13:-250--200</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>-300--270</t>
+          <t>-250--200</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9098,17 +9098,17 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>14:0-10</t>
+          <t>Ho:13:-270--250</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>-270--250</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
@@ -9133,7 +9133,7 @@
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9150,17 +9150,17 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>14:-10-0</t>
+          <t>Ho:13:-300--270</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>-10-0</t>
+          <t>-300--270</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>14:-20--10</t>
+          <t>Hu:14:0-10</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>-20--10</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
@@ -9237,7 +9237,7 @@
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9254,17 +9254,17 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>14:-30--20</t>
+          <t>Ho:14:-10-0</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>-30--20</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -9289,7 +9289,7 @@
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9306,17 +9306,17 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>14:-40--30</t>
+          <t>Ho:14:-20--10</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>-40--30</t>
+          <t>-20--10</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
@@ -9341,7 +9341,7 @@
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9358,17 +9358,17 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>14:-50--40</t>
+          <t>Ho:14:-30--20</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>-50--40</t>
+          <t>-30--20</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -9393,7 +9393,7 @@
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9410,17 +9410,17 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>14:-60--50</t>
+          <t>Ho:14:-40--30</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>-60--50</t>
+          <t>-40--30</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
@@ -9445,7 +9445,7 @@
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9462,17 +9462,17 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>14:-70--60</t>
+          <t>Ho:14:-50--40</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>-70--60</t>
+          <t>-50--40</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -9497,7 +9497,7 @@
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9514,17 +9514,17 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>14:-80--70</t>
+          <t>Ho:14:-60--50</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>-80--70</t>
+          <t>-60--50</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
@@ -9549,7 +9549,7 @@
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9566,17 +9566,17 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>14:-90--80</t>
+          <t>Ho:14:-70--60</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>-90--80</t>
+          <t>-70--60</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
@@ -9601,7 +9601,7 @@
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9618,17 +9618,17 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>14:-100--90</t>
+          <t>Ho:14:-80--70</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>-100--90</t>
+          <t>-80--70</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
@@ -9653,7 +9653,7 @@
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9670,17 +9670,17 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>14:-125--100</t>
+          <t>Ho:14:-90--80</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>-125--100</t>
+          <t>-90--80</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -9705,7 +9705,7 @@
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9722,17 +9722,17 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>14:-150--125</t>
+          <t>Ho:14:-100--90</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>-150--125</t>
+          <t>-100--90</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
@@ -9757,7 +9757,7 @@
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9774,17 +9774,17 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>14:-175--150</t>
+          <t>Ho:14:-125--100</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>-175--150</t>
+          <t>-125--100</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9826,17 +9826,17 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>14:-200--175</t>
+          <t>Ho:14:-150--125</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>-200--175</t>
+          <t>-150--125</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
@@ -9861,7 +9861,7 @@
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9878,17 +9878,17 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>14:-215--200</t>
+          <t>Ho:14:-175--150</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>-215--200</t>
+          <t>-175--150</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -9913,7 +9913,7 @@
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9930,17 +9930,17 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>14:-220--215</t>
+          <t>Ho:14:-200--175</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>-220--215</t>
+          <t>-200--175</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
@@ -9965,7 +9965,7 @@
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9982,22 +9982,22 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>15:20-24</t>
+          <t>Ho:14:-215--200</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>-215--200</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>2012-08-15</t>
+          <t>2012-08-14</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -10017,7 +10017,7 @@
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10034,22 +10034,22 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>15:10-20</t>
+          <t>Ho:14:-220--215</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>-220--215</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>2012-08-15</t>
+          <t>2012-08-14</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -10069,7 +10069,7 @@
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10086,17 +10086,17 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>15:0-10</t>
+          <t>Hu:15:20-24</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>20-24</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -10121,7 +10121,7 @@
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10138,17 +10138,17 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Hu:15:10-20</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>-10-0</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10190,17 +10190,17 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>15:-20--10</t>
+          <t>Hu:15:0-10</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>-20--10</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -10225,7 +10225,7 @@
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10242,17 +10242,17 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>15:-30--20</t>
+          <t>Hu:15:-10-0</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>-30--20</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
@@ -10277,7 +10277,7 @@
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10294,17 +10294,17 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>15:-40--30</t>
+          <t>Ho:15:-10-0</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>-40--30</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
@@ -10329,7 +10329,7 @@
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10346,17 +10346,17 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>15:-50--40</t>
+          <t>Ho:15:-20--10</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>-50--40</t>
+          <t>-20--10</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
@@ -10381,7 +10381,7 @@
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10398,17 +10398,17 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>15:-60--50</t>
+          <t>Ho:15:-30--20</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>-60--50</t>
+          <t>-30--20</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
@@ -10433,7 +10433,7 @@
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10450,17 +10450,17 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>15:-70--60</t>
+          <t>Ho:15:-40--30</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>-70--60</t>
+          <t>-40--30</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
@@ -10485,7 +10485,7 @@
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10502,17 +10502,17 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>15:-80--70</t>
+          <t>Ho:15:-50--40</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>-80--70</t>
+          <t>-50--40</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
@@ -10537,7 +10537,7 @@
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10554,17 +10554,17 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>15:-90--80</t>
+          <t>Ho:15:-60--50</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>-90--80</t>
+          <t>-60--50</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
@@ -10589,7 +10589,7 @@
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10606,17 +10606,17 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>15:-100--90</t>
+          <t>Ho:15:-70--60</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>-100--90</t>
+          <t>-70--60</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
@@ -10641,7 +10641,7 @@
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10658,17 +10658,17 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>15:-125--100</t>
+          <t>Ho:15:-80--70</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>-125--100</t>
+          <t>-80--70</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
@@ -10693,7 +10693,7 @@
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10710,17 +10710,17 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>15:-150--125</t>
+          <t>Ho:15:-90--80</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>-150--125</t>
+          <t>-90--80</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
@@ -10745,7 +10745,7 @@
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10762,17 +10762,17 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>16:20-29</t>
+          <t>Ho:15:-100--90</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>20-29</t>
+          <t>-100--90</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10814,17 +10814,17 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>16:10-20</t>
+          <t>Ho:15:-125--100</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>-125--100</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
@@ -10849,7 +10849,7 @@
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10866,17 +10866,17 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>16:0-10</t>
+          <t>Ho:15:-150--125</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>-150--125</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
@@ -10901,7 +10901,7 @@
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10918,17 +10918,17 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Hu:16:20-29</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>-10-0</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
@@ -10953,7 +10953,7 @@
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10970,17 +10970,17 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>16:-20--10</t>
+          <t>Hu:16:10-20</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>-20--10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
@@ -11005,7 +11005,7 @@
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11022,17 +11022,17 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>16:-30--20</t>
+          <t>Hu:16:0-10</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>-30--20</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11074,17 +11074,17 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>16:-40--30</t>
+          <t>Hu:16:-10-0</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>-40--30</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11126,17 +11126,17 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>16:-50--40</t>
+          <t>Ho:16:-10-0</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>-50--40</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
@@ -11161,7 +11161,7 @@
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11178,17 +11178,17 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>16:-60--50</t>
+          <t>Ho:16:-20--10</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>-60--50</t>
+          <t>-20--10</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
@@ -11213,7 +11213,7 @@
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11230,17 +11230,17 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>16:-70--60</t>
+          <t>Ho:16:-30--20</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>-70--60</t>
+          <t>-30--20</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
@@ -11265,7 +11265,7 @@
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11282,17 +11282,17 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>16:-80--70</t>
+          <t>Ho:16:-40--30</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>-80--70</t>
+          <t>-40--30</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
@@ -11317,7 +11317,7 @@
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11334,17 +11334,17 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>16:-90--80</t>
+          <t>Ho:16:-50--40</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>-90--80</t>
+          <t>-50--40</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
@@ -11369,7 +11369,7 @@
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11386,17 +11386,17 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>16:-100--90</t>
+          <t>Ho:16:-60--50</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>-100--90</t>
+          <t>-60--50</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
@@ -11421,7 +11421,7 @@
       <c r="K211" s="2" t="inlineStr"/>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11438,17 +11438,17 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>16:-125--100</t>
+          <t>Ho:16:-70--60</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>-125--100</t>
+          <t>-70--60</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
@@ -11473,7 +11473,7 @@
       <c r="K212" s="2" t="inlineStr"/>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11490,17 +11490,17 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>16:-150--125</t>
+          <t>Ho:16:-80--70</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>-150--125</t>
+          <t>-80--70</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
@@ -11525,7 +11525,7 @@
       <c r="K213" s="2" t="inlineStr"/>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11542,17 +11542,17 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>16:-175--150</t>
+          <t>Ho:16:-90--80</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>-175--150</t>
+          <t>-90--80</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
@@ -11577,7 +11577,7 @@
       <c r="K214" s="2" t="inlineStr"/>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11594,17 +11594,17 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>16:-200--175</t>
+          <t>Ho:16:-100--90</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>-200--175</t>
+          <t>-100--90</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       <c r="K215" s="2" t="inlineStr"/>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11646,17 +11646,17 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>16:-250--200</t>
+          <t>Ho:16:-125--100</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>-250--200</t>
+          <t>-125--100</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
@@ -11681,7 +11681,7 @@
       <c r="K216" s="2" t="inlineStr"/>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11698,17 +11698,17 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>17:20-25</t>
+          <t>Ho:16:-150--125</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>20-25</t>
+          <t>-150--125</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
@@ -11733,7 +11733,7 @@
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11750,17 +11750,17 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>17:10-20</t>
+          <t>Ho:16:-175--150</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>-175--150</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
@@ -11785,7 +11785,7 @@
       <c r="K218" s="2" t="inlineStr"/>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11802,17 +11802,17 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>17:0-10</t>
+          <t>Ho:16:-200--175</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>-200--175</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
@@ -11837,7 +11837,7 @@
       <c r="K219" s="2" t="inlineStr"/>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11854,17 +11854,17 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Ho:16:-250--200</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>-10-0</t>
+          <t>-250--200</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
@@ -11889,7 +11889,7 @@
       <c r="K220" s="2" t="inlineStr"/>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11906,17 +11906,17 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>17:-20--10</t>
+          <t>Hu:17:20-25</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>-20--10</t>
+          <t>20-25</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
@@ -11941,7 +11941,7 @@
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11958,17 +11958,17 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>17:-30--20</t>
+          <t>Hu:17:10-20</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>-30--20</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
@@ -11993,7 +11993,7 @@
       <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12010,17 +12010,17 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>17:-40--30</t>
+          <t>Hu:17:0-10</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>-40--30</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
@@ -12045,7 +12045,7 @@
       <c r="K223" s="2" t="inlineStr"/>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12062,17 +12062,17 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>17:-50--40</t>
+          <t>Hu:17:-10-0</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>-50--40</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
@@ -12097,7 +12097,7 @@
       <c r="K224" s="2" t="inlineStr"/>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12114,17 +12114,17 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>17:-60--50</t>
+          <t>Ho:17:-10-0</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>-60--50</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       <c r="K225" s="2" t="inlineStr"/>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12166,17 +12166,17 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>17:-70--60</t>
+          <t>Ho:17:-20--10</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>-70--60</t>
+          <t>-20--10</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
@@ -12201,7 +12201,7 @@
       <c r="K226" s="2" t="inlineStr"/>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12218,17 +12218,17 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>17:-80--70</t>
+          <t>Ho:17:-30--20</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>-80--70</t>
+          <t>-30--20</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
@@ -12253,7 +12253,7 @@
       <c r="K227" s="2" t="inlineStr"/>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12270,17 +12270,17 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>17:-90--80</t>
+          <t>Ho:17:-40--30</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>-90--80</t>
+          <t>-40--30</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
@@ -12305,7 +12305,7 @@
       <c r="K228" s="2" t="inlineStr"/>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12322,17 +12322,17 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>17:-100--90</t>
+          <t>Ho:17:-50--40</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>-100--90</t>
+          <t>-50--40</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
@@ -12357,7 +12357,7 @@
       <c r="K229" s="2" t="inlineStr"/>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12374,17 +12374,17 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>17:-125--100</t>
+          <t>Ho:17:-60--50</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>-125--100</t>
+          <t>-60--50</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
@@ -12409,7 +12409,7 @@
       <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12426,17 +12426,17 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>17:-150--125</t>
+          <t>Ho:17:-70--60</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>-150--125</t>
+          <t>-70--60</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
@@ -12461,7 +12461,7 @@
       <c r="K231" s="2" t="inlineStr"/>
       <c r="L231" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12478,17 +12478,17 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>17:-175--150</t>
+          <t>Ho:17:-80--70</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>-175--150</t>
+          <t>-80--70</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
@@ -12513,7 +12513,7 @@
       <c r="K232" s="2" t="inlineStr"/>
       <c r="L232" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12530,17 +12530,17 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>17:-200--175</t>
+          <t>Ho:17:-90--80</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>-200--175</t>
+          <t>-90--80</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
@@ -12565,7 +12565,7 @@
       <c r="K233" s="2" t="inlineStr"/>
       <c r="L233" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12582,17 +12582,17 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>17:-239--200</t>
+          <t>Ho:17:-100--90</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>-239--200</t>
+          <t>-100--90</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
@@ -12617,7 +12617,7 @@
       <c r="K234" s="2" t="inlineStr"/>
       <c r="L234" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12634,17 +12634,17 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>19:10-20</t>
+          <t>Ho:17:-125--100</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>-125--100</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
@@ -12669,7 +12669,7 @@
       <c r="K235" s="2" t="inlineStr"/>
       <c r="L235" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12686,17 +12686,17 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>19:0-10</t>
+          <t>Ho:17:-150--125</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>-150--125</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
@@ -12721,7 +12721,7 @@
       <c r="K236" s="2" t="inlineStr"/>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12738,17 +12738,17 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>19:-10-0</t>
+          <t>Ho:17:-175--150</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>-10-0</t>
+          <t>-175--150</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
@@ -12773,7 +12773,7 @@
       <c r="K237" s="2" t="inlineStr"/>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12790,17 +12790,17 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>19:-20--10</t>
+          <t>Ho:17:-200--175</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>-20--10</t>
+          <t>-200--175</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
@@ -12825,7 +12825,7 @@
       <c r="K238" s="2" t="inlineStr"/>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12842,17 +12842,17 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>19:-30--20</t>
+          <t>Ho:17:-239--200</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>-30--20</t>
+          <t>-239--200</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
@@ -12877,7 +12877,7 @@
       <c r="K239" s="2" t="inlineStr"/>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12894,17 +12894,17 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>19:-40--30</t>
+          <t>Hu:19:10-20</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>-40--30</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
@@ -12929,7 +12929,7 @@
       <c r="K240" s="2" t="inlineStr"/>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12946,17 +12946,17 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>19:-50--40</t>
+          <t>Hu:19:0-10</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>-50--40</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
@@ -12981,7 +12981,7 @@
       <c r="K241" s="2" t="inlineStr"/>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12998,17 +12998,17 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>19:-60--50</t>
+          <t>Ho:19:-10-0</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>-60--50</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
@@ -13033,7 +13033,7 @@
       <c r="K242" s="2" t="inlineStr"/>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13050,17 +13050,17 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>19:-70--60</t>
+          <t>Ho:19:-20--10</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>-70--60</t>
+          <t>-20--10</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
@@ -13085,7 +13085,7 @@
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13102,17 +13102,17 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>19:-80--70</t>
+          <t>Ho:19:-30--20</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>-80--70</t>
+          <t>-30--20</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
@@ -13137,7 +13137,7 @@
       <c r="K244" s="2" t="inlineStr"/>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13154,17 +13154,17 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>19:-90--80</t>
+          <t>Ho:19:-40--30</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>-90--80</t>
+          <t>-40--30</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
@@ -13189,7 +13189,7 @@
       <c r="K245" s="2" t="inlineStr"/>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13206,17 +13206,17 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>19:-100--90</t>
+          <t>Ho:19:-50--40</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>-100--90</t>
+          <t>-50--40</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
@@ -13241,7 +13241,7 @@
       <c r="K246" s="2" t="inlineStr"/>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13258,17 +13258,17 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>19:-125--100</t>
+          <t>Ho:19:-60--50</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>-125--100</t>
+          <t>-60--50</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
@@ -13293,7 +13293,7 @@
       <c r="K247" s="2" t="inlineStr"/>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13310,17 +13310,17 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>19:-150--125</t>
+          <t>Ho:19:-70--60</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>-150--125</t>
+          <t>-70--60</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
@@ -13345,7 +13345,7 @@
       <c r="K248" s="2" t="inlineStr"/>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13362,17 +13362,17 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>19:-175--150</t>
+          <t>Ho:19:-80--70</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>-175--150</t>
+          <t>-80--70</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
@@ -13397,7 +13397,7 @@
       <c r="K249" s="2" t="inlineStr"/>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13414,17 +13414,17 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>19:-200--175</t>
+          <t>Ho:19:-90--80</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>-200--175</t>
+          <t>-90--80</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
@@ -13449,7 +13449,7 @@
       <c r="K250" s="2" t="inlineStr"/>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13466,17 +13466,17 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>19:-216--200</t>
+          <t>Ho:19:-100--90</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>-216--200</t>
+          <t>-100--90</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
@@ -13501,7 +13501,7 @@
       <c r="K251" s="2" t="inlineStr"/>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13518,17 +13518,17 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>19:-250--216</t>
+          <t>Ho:19:-125--100</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>-250--216</t>
+          <t>-125--100</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
@@ -13553,7 +13553,7 @@
       <c r="K252" s="2" t="inlineStr"/>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13570,17 +13570,17 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>20:10-19</t>
+          <t>Ho:19:-150--125</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>10-19</t>
+          <t>-150--125</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
@@ -13605,7 +13605,7 @@
       <c r="K253" s="2" t="inlineStr"/>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13622,17 +13622,17 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>20:0-10</t>
+          <t>Ho:19:-175--150</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>-175--150</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
@@ -13657,7 +13657,7 @@
       <c r="K254" s="2" t="inlineStr"/>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13674,17 +13674,17 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Ho:19:-200--175</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>-10-0</t>
+          <t>-200--175</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
@@ -13709,7 +13709,7 @@
       <c r="K255" s="2" t="inlineStr"/>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13726,17 +13726,17 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>20:-20--10</t>
+          <t>Ho:19:-216--200</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>-20--10</t>
+          <t>-216--200</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
@@ -13761,7 +13761,7 @@
       <c r="K256" s="2" t="inlineStr"/>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13778,17 +13778,17 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>20:-30--20</t>
+          <t>Ho:19:-250--216</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>-30--20</t>
+          <t>-250--216</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
@@ -13813,7 +13813,7 @@
       <c r="K257" s="2" t="inlineStr"/>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13830,17 +13830,17 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>20:-40--30</t>
+          <t>Hu:20:10-19</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>-40--30</t>
+          <t>10-19</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
@@ -13865,7 +13865,7 @@
       <c r="K258" s="2" t="inlineStr"/>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13882,17 +13882,17 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>20:-50--40</t>
+          <t>Hu:20:0-10</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>-50--40</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
@@ -13917,7 +13917,7 @@
       <c r="K259" s="2" t="inlineStr"/>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13934,17 +13934,17 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>20:-60--50</t>
+          <t>Hu:20:-10-0</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>-60--50</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
@@ -13969,7 +13969,7 @@
       <c r="K260" s="2" t="inlineStr"/>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13986,17 +13986,17 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>20:-70--60</t>
+          <t>Ho:20:-10-0</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>-70--60</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
@@ -14021,7 +14021,7 @@
       <c r="K261" s="2" t="inlineStr"/>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14038,17 +14038,17 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>20:-80--70</t>
+          <t>Ho:20:-20--10</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>-80--70</t>
+          <t>-20--10</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
@@ -14073,7 +14073,7 @@
       <c r="K262" s="2" t="inlineStr"/>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14090,17 +14090,17 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>20:-90--80</t>
+          <t>Ho:20:-30--20</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>-90--80</t>
+          <t>-30--20</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
@@ -14125,7 +14125,7 @@
       <c r="K263" s="2" t="inlineStr"/>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14142,17 +14142,17 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>20:-100--90</t>
+          <t>Ho:20:-40--30</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>-100--90</t>
+          <t>-40--30</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
@@ -14177,7 +14177,7 @@
       <c r="K264" s="2" t="inlineStr"/>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14194,17 +14194,17 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>20:-125--100</t>
+          <t>Ho:20:-50--40</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>-125--100</t>
+          <t>-50--40</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
@@ -14229,7 +14229,7 @@
       <c r="K265" s="2" t="inlineStr"/>
       <c r="L265" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14246,17 +14246,17 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>20:-150--125</t>
+          <t>Ho:20:-60--50</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>-150--125</t>
+          <t>-60--50</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
@@ -14281,7 +14281,7 @@
       <c r="K266" s="2" t="inlineStr"/>
       <c r="L266" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14298,17 +14298,17 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>20:-175--150</t>
+          <t>Ho:20:-70--60</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>-175--150</t>
+          <t>-70--60</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
@@ -14333,7 +14333,7 @@
       <c r="K267" s="2" t="inlineStr"/>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14350,17 +14350,17 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>20:-200--175</t>
+          <t>Ho:20:-80--70</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>-200--175</t>
+          <t>-80--70</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
@@ -14385,7 +14385,7 @@
       <c r="K268" s="2" t="inlineStr"/>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14402,17 +14402,17 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>20:-250--200</t>
+          <t>Ho:20:-90--80</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>-250--200</t>
+          <t>-90--80</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
@@ -14437,7 +14437,7 @@
       <c r="K269" s="2" t="inlineStr"/>
       <c r="L269" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14454,17 +14454,17 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>20:-300--250</t>
+          <t>Ho:20:-100--90</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>-300--250</t>
+          <t>-100--90</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
@@ -14489,7 +14489,7 @@
       <c r="K270" s="2" t="inlineStr"/>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14506,17 +14506,17 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>21:10-20</t>
+          <t>Ho:20:-125--100</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>-125--100</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
@@ -14541,7 +14541,7 @@
       <c r="K271" s="2" t="inlineStr"/>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14558,17 +14558,17 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>21:0-10</t>
+          <t>Ho:20:-150--125</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>-150--125</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
@@ -14593,7 +14593,7 @@
       <c r="K272" s="2" t="inlineStr"/>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14610,17 +14610,17 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>21:-10-0</t>
+          <t>Ho:20:-175--150</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>-10-0</t>
+          <t>-175--150</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
@@ -14645,7 +14645,7 @@
       <c r="K273" s="2" t="inlineStr"/>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14662,17 +14662,17 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>21:-20--10</t>
+          <t>Ho:20:-200--175</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>-20--10</t>
+          <t>-200--175</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
@@ -14697,7 +14697,7 @@
       <c r="K274" s="2" t="inlineStr"/>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14714,17 +14714,17 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>21:-30--20</t>
+          <t>Ho:20:-250--200</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>-30--20</t>
+          <t>-250--200</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
@@ -14749,7 +14749,7 @@
       <c r="K275" s="2" t="inlineStr"/>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14766,17 +14766,17 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>21:-40--30</t>
+          <t>Ho:20:-300--250</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>-40--30</t>
+          <t>-300--250</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
@@ -14801,7 +14801,7 @@
       <c r="K276" s="2" t="inlineStr"/>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14818,17 +14818,17 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>21:-50--40</t>
+          <t>Hu:21:10-20</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>-50--40</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr">
@@ -14853,7 +14853,7 @@
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14870,17 +14870,17 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>21:-60--50</t>
+          <t>Hu:21:0-10</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>-60--50</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
@@ -14905,7 +14905,7 @@
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14922,17 +14922,17 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>21:-70--60</t>
+          <t>Ho:21:-10-0</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>-70--60</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
@@ -14957,7 +14957,7 @@
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14974,17 +14974,17 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>21:-80--70</t>
+          <t>Ho:21:-20--10</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>-80--70</t>
+          <t>-20--10</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
@@ -15009,7 +15009,7 @@
       <c r="K280" s="2" t="inlineStr"/>
       <c r="L280" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15026,17 +15026,17 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>21:-90--80</t>
+          <t>Ho:21:-30--20</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>-90--80</t>
+          <t>-30--20</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr">
@@ -15061,7 +15061,7 @@
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15078,17 +15078,17 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>21:-100--90</t>
+          <t>Ho:21:-40--30</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>-100--90</t>
+          <t>-40--30</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
@@ -15113,7 +15113,7 @@
       <c r="K282" s="2" t="inlineStr"/>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15130,17 +15130,17 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>21:-125--100</t>
+          <t>Ho:21:-50--40</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>-125--100</t>
+          <t>-50--40</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
@@ -15165,7 +15165,7 @@
       <c r="K283" s="2" t="inlineStr"/>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15182,17 +15182,17 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>21:-150--125</t>
+          <t>Ho:21:-60--50</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>-150--125</t>
+          <t>-60--50</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
@@ -15217,7 +15217,7 @@
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15234,17 +15234,17 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>21:-175--150</t>
+          <t>Ho:21:-70--60</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>-175--150</t>
+          <t>-70--60</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
@@ -15269,7 +15269,7 @@
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15286,17 +15286,17 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>21:-200--175</t>
+          <t>Ho:21:-80--70</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>-200--175</t>
+          <t>-80--70</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
@@ -15321,7 +15321,7 @@
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15338,26 +15338,26 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>21:-250--200</t>
+          <t>Ho:21:-90--80</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>-250--200</t>
+          <t>-90--80</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>2011-12-15</t>
+          <t>2012-08-15</t>
         </is>
       </c>
       <c r="G287" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -15373,7 +15373,319 @@
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>doi:10.3334/CDIAC/SPRUCE.005</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>Peat_Characteristics_T0_20180425.csv</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>Ho:21:-100--90</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>Topography:Plot:depth</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>-100--90</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>2012-08-15</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>0</v>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I288" t="n">
+        <v>47.5056</v>
+      </c>
+      <c r="J288" t="n">
+        <v>-93.45328000000001</v>
+      </c>
+      <c r="K288" s="2" t="inlineStr"/>
+      <c r="L288" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>doi:10.3334/CDIAC/SPRUCE.005</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>Peat_Characteristics_T0_20180425.csv</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>Ho:21:-125--100</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>Topography:Plot:depth</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>-125--100</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>2012-08-15</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I289" t="n">
+        <v>47.5056</v>
+      </c>
+      <c r="J289" t="n">
+        <v>-93.45328000000001</v>
+      </c>
+      <c r="K289" s="2" t="inlineStr"/>
+      <c r="L289" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>doi:10.3334/CDIAC/SPRUCE.005</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>Peat_Characteristics_T0_20180425.csv</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>Ho:21:-150--125</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>Topography:Plot:depth</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>-150--125</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>2012-08-15</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>0</v>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I290" t="n">
+        <v>47.5056</v>
+      </c>
+      <c r="J290" t="n">
+        <v>-93.45328000000001</v>
+      </c>
+      <c r="K290" s="2" t="inlineStr"/>
+      <c r="L290" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>doi:10.3334/CDIAC/SPRUCE.005</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>Peat_Characteristics_T0_20180425.csv</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>Ho:21:-175--150</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>Topography:Plot:depth</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>-175--150</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>2012-08-15</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>0</v>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I291" t="n">
+        <v>47.5056</v>
+      </c>
+      <c r="J291" t="n">
+        <v>-93.45328000000001</v>
+      </c>
+      <c r="K291" s="2" t="inlineStr"/>
+      <c r="L291" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>doi:10.3334/CDIAC/SPRUCE.005</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>Peat_Characteristics_T0_20180425.csv</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>Ho:21:-200--175</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>Topography:Plot:depth</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>-200--175</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>2012-08-15</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>0</v>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I292" t="n">
+        <v>47.5056</v>
+      </c>
+      <c r="J292" t="n">
+        <v>-93.45328000000001</v>
+      </c>
+      <c r="K292" s="2" t="inlineStr"/>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>doi:10.3334/CDIAC/SPRUCE.005</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>Peat_Characteristics_T0_20180425.csv</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>Ho:21:-250--200</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>Topography:Plot:depth</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>-250--200</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>2011-12-15</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I293" t="n">
+        <v>47.5056</v>
+      </c>
+      <c r="J293" t="n">
+        <v>-93.45328000000001</v>
+      </c>
+      <c r="K293" s="2" t="inlineStr"/>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cd (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
